--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T11:44:16+00:00</t>
+    <t>2026-07-15T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T12:32:02+00:00</t>
+    <t>2026-07-15T14:55:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T14:55:56+00:00</t>
+    <t>2026-07-16T09:23:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$74</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2806" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2844" uniqueCount="505">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T09:23:28+00:00</t>
+    <t>2026-07-17T06:35:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -657,6 +657,22 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>Condition.extension:entered-in-error</t>
+  </si>
+  <si>
+    <t>entered-in-error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-ext-entered-in-error}
+</t>
+  </si>
+  <si>
+    <t>AT ELGA Entered In Error</t>
+  </si>
+  <si>
+    <t>Kennzeichnet, ob eine Information fehlerhaft eingegeben wurde.</t>
   </si>
   <si>
     <t>Condition.modifierExtension</t>
@@ -1903,12 +1919,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP73"/>
+  <dimension ref="A1:AP74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.85546875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="30.765625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="13.48828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -4230,43 +4246,41 @@
         <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>112</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -4314,7 +4328,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4323,7 +4337,7 @@
         <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>120</v>
@@ -4338,7 +4352,7 @@
         <v>21</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>21</v>
@@ -4356,38 +4370,38 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -4436,7 +4450,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4448,10 +4462,10 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>217</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
@@ -4460,21 +4474,21 @@
         <v>21</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4482,33 +4496,35 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4532,13 +4548,13 @@
         <v>21</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>21</v>
@@ -4556,34 +4572,34 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>229</v>
+        <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>21</v>
@@ -4591,10 +4607,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4617,16 +4633,16 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4655,10 +4671,10 @@
         <v>164</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4676,7 +4692,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4685,36 +4701,36 @@
         <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4722,31 +4738,31 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4772,13 +4788,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4796,45 +4812,45 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI24" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4857,16 +4873,16 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4892,13 +4908,13 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
@@ -4916,13 +4932,13 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
@@ -4934,61 +4950,61 @@
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AP25" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" hidden="true">
+      <c r="A26" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AM25" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>263</v>
-      </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>264</v>
+        <v>21</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -5012,13 +5028,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -5036,7 +5052,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5051,62 +5067,64 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>21</v>
+        <v>269</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>105</v>
+        <v>226</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>106</v>
+        <v>270</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>107</v>
+        <v>271</v>
       </c>
       <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -5130,13 +5148,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -5154,7 +5172,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>108</v>
+        <v>268</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5166,44 +5184,44 @@
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>21</v>
+        <v>275</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>109</v>
+        <v>278</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>21</v>
+        <v>279</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
@@ -5215,17 +5233,15 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -5262,31 +5278,31 @@
         <v>21</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>21</v>
@@ -5309,21 +5325,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>279</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -5332,23 +5348,21 @@
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>280</v>
+        <v>113</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>281</v>
+        <v>114</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -5384,17 +5398,19 @@
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AC29" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>285</v>
+        <v>118</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>286</v>
+        <v>119</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5406,7 +5422,7 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
@@ -5415,10 +5431,10 @@
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>287</v>
+        <v>21</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>288</v>
+        <v>109</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>21</v>
@@ -5429,14 +5445,12 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5445,7 +5459,7 @@
         <v>91</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>284</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -5460,16 +5474,16 @@
         <v>145</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5506,19 +5520,17 @@
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5539,10 +5551,10 @@
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>21</v>
@@ -5553,18 +5565,20 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>91</v>
@@ -5576,19 +5590,23 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>106</v>
+        <v>285</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5636,19 +5654,19 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>108</v>
+        <v>291</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>21</v>
@@ -5657,10 +5675,10 @@
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>109</v>
+        <v>293</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>21</v>
@@ -5671,21 +5689,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5697,17 +5715,15 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5744,31 +5760,31 @@
         <v>21</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
@@ -5791,21 +5807,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5814,29 +5830,27 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>297</v>
+        <v>113</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>298</v>
+        <v>114</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>301</v>
+        <v>21</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>21</v>
@@ -5866,31 +5880,31 @@
         <v>21</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>302</v>
+        <v>119</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
@@ -5899,10 +5913,10 @@
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>303</v>
+        <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>304</v>
+        <v>109</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>21</v>
@@ -5913,10 +5927,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5924,7 +5938,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>91</v>
@@ -5939,24 +5953,26 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>21</v>
+        <v>306</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>21</v>
@@ -5998,7 +6014,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6019,10 +6035,10 @@
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
@@ -6033,10 +6049,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6044,7 +6060,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>91</v>
@@ -6059,18 +6075,18 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>172</v>
+        <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -6118,7 +6134,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6139,10 +6155,10 @@
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>21</v>
@@ -6153,10 +6169,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6164,7 +6180,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>91</v>
@@ -6179,17 +6195,17 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -6238,7 +6254,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6259,10 +6275,10 @@
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
@@ -6273,10 +6289,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6299,19 +6315,17 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>331</v>
+        <v>105</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6360,7 +6374,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6381,10 +6395,10 @@
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -6395,14 +6409,12 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6423,19 +6435,19 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>145</v>
+        <v>336</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>281</v>
+        <v>338</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>282</v>
+        <v>339</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>283</v>
+        <v>340</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6484,13 +6496,13 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
@@ -6505,10 +6517,10 @@
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>287</v>
+        <v>342</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>288</v>
+        <v>343</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
@@ -6519,12 +6531,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6542,19 +6556,23 @@
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>106</v>
+        <v>285</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6602,19 +6620,19 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>108</v>
+        <v>291</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>21</v>
@@ -6623,10 +6641,10 @@
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>109</v>
+        <v>293</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
@@ -6637,21 +6655,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
@@ -6663,17 +6681,15 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6710,31 +6726,31 @@
         <v>21</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
@@ -6757,21 +6773,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6780,29 +6796,27 @@
         <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>297</v>
+        <v>113</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>298</v>
+        <v>114</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>344</v>
+        <v>21</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>21</v>
@@ -6832,31 +6846,31 @@
         <v>21</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>302</v>
+        <v>119</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
@@ -6865,10 +6879,10 @@
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>303</v>
+        <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>304</v>
+        <v>109</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
@@ -6879,10 +6893,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6890,7 +6904,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>91</v>
@@ -6905,24 +6919,26 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>21</v>
+        <v>349</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>21</v>
@@ -6964,7 +6980,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6985,10 +7001,10 @@
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
@@ -6999,10 +7015,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7010,7 +7026,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>91</v>
@@ -7025,18 +7041,18 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>172</v>
+        <v>105</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -7084,7 +7100,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7105,10 +7121,10 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>21</v>
@@ -7119,10 +7135,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7130,7 +7146,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>91</v>
@@ -7145,17 +7161,17 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -7204,7 +7220,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7225,10 +7241,10 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -7239,10 +7255,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7265,19 +7281,17 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>331</v>
+        <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7326,7 +7340,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7347,10 +7361,10 @@
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -7361,10 +7375,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7375,7 +7389,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -7387,19 +7401,19 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>105</v>
+        <v>336</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7448,7 +7462,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7469,10 +7483,10 @@
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>21</v>
@@ -7483,10 +7497,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7509,18 +7523,20 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>221</v>
+        <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="O47" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M47" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7544,13 +7560,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>361</v>
+        <v>21</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>362</v>
+        <v>21</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7568,13 +7584,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -7586,41 +7602,41 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>363</v>
+        <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>365</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>367</v>
+        <v>21</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
@@ -7629,18 +7645,18 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>368</v>
+        <v>226</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -7664,13 +7680,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>21</v>
+        <v>366</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>21</v>
+        <v>367</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7688,13 +7704,13 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
@@ -7703,44 +7719,44 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>372</v>
+        <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>21</v>
+        <v>368</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>373</v>
+        <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>21</v>
+        <v>370</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>21</v>
+        <v>372</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
@@ -7749,18 +7765,18 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7808,10 +7824,10 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>91</v>
@@ -7823,19 +7839,19 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>21</v>
@@ -7843,10 +7859,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7857,7 +7873,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
@@ -7869,16 +7885,16 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7928,7 +7944,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7943,19 +7959,19 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>21</v>
@@ -7963,10 +7979,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7986,19 +8002,19 @@
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8048,7 +8064,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8057,36 +8073,36 @@
         <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>398</v>
+        <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>21</v>
+        <v>396</v>
       </c>
       <c r="AN51" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AO51" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>401</v>
-      </c>
       <c r="B52" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8094,30 +8110,32 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8166,7 +8184,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8175,7 +8193,7 @@
         <v>91</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>21</v>
+        <v>403</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>103</v>
@@ -8187,13 +8205,13 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>21</v>
@@ -8201,10 +8219,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8227,13 +8245,13 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8284,7 +8302,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8305,24 +8323,24 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>21</v>
+        <v>409</v>
       </c>
       <c r="AN53" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AO53" t="s" s="2">
+      <c r="AP53" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AP53" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>413</v>
-      </c>
       <c r="B54" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8330,13 +8348,13 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
@@ -8345,13 +8363,13 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8402,7 +8420,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8423,13 +8441,13 @@
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>21</v>
@@ -8437,10 +8455,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8451,7 +8469,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
@@ -8460,16 +8478,16 @@
         <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8520,34 +8538,34 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>21</v>
@@ -8555,10 +8573,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8569,7 +8587,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
@@ -8581,13 +8599,13 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>105</v>
+        <v>426</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>106</v>
+        <v>427</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>107</v>
+        <v>428</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8638,19 +8656,19 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>108</v>
+        <v>425</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>21</v>
+        <v>429</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
@@ -8662,7 +8680,7 @@
         <v>21</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>109</v>
+        <v>430</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>21</v>
@@ -8673,21 +8691,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -8699,17 +8717,15 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8758,19 +8774,19 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
@@ -8793,14 +8809,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>429</v>
+        <v>111</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8813,26 +8829,24 @@
         <v>21</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>430</v>
+        <v>113</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>431</v>
+        <v>114</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O58" t="s" s="2">
-        <v>209</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8880,7 +8894,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>432</v>
+        <v>119</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8904,7 +8918,7 @@
         <v>21</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>
@@ -8922,35 +8936,39 @@
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>221</v>
+        <v>112</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8974,55 +8992,55 @@
         <v>21</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>436</v>
+        <v>21</v>
       </c>
       <c r="Z59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AA59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>433</v>
-      </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>439</v>
+        <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>273</v>
+        <v>195</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>21</v>
@@ -9033,10 +9051,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9047,7 +9065,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
@@ -9059,13 +9077,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>441</v>
+        <v>226</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9092,13 +9110,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>21</v>
+        <v>441</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9116,16 +9134,16 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>103</v>
@@ -9134,13 +9152,13 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>21</v>
+        <v>444</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>21</v>
+        <v>235</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>444</v>
+        <v>278</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>21</v>
@@ -9165,7 +9183,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -9177,13 +9195,13 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>221</v>
+        <v>446</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9210,13 +9228,13 @@
         <v>21</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>448</v>
+        <v>21</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>21</v>
@@ -9240,10 +9258,10 @@
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>21</v>
+        <v>443</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>103</v>
@@ -9258,7 +9276,7 @@
         <v>21</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>21</v>
@@ -9269,10 +9287,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9283,7 +9301,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -9295,17 +9313,15 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>421</v>
+        <v>226</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M62" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>454</v>
-      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9330,13 +9346,13 @@
         <v>21</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>21</v>
+        <v>453</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
@@ -9354,31 +9370,31 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>21</v>
@@ -9389,10 +9405,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9403,7 +9419,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
@@ -9415,15 +9431,17 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>105</v>
+        <v>426</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>106</v>
+        <v>457</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9472,19 +9490,19 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>108</v>
+        <v>456</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>21</v>
+        <v>460</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
@@ -9496,7 +9514,7 @@
         <v>21</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>109</v>
+        <v>461</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>21</v>
@@ -9507,21 +9525,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>21</v>
@@ -9533,17 +9551,15 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -9592,19 +9608,19 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
@@ -9627,14 +9643,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>429</v>
+        <v>111</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9647,26 +9663,24 @@
         <v>21</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>430</v>
+        <v>113</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>431</v>
+        <v>114</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O65" t="s" s="2">
-        <v>209</v>
-      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9714,7 +9728,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>432</v>
+        <v>119</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9738,7 +9752,7 @@
         <v>21</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>21</v>
@@ -9749,14 +9763,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9769,22 +9783,26 @@
         <v>21</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>221</v>
+        <v>112</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>461</v>
+        <v>435</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9808,13 +9826,13 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>463</v>
+        <v>21</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>464</v>
+        <v>21</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -9832,7 +9850,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>460</v>
+        <v>437</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9841,25 +9859,25 @@
         <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>465</v>
+        <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>466</v>
+        <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>467</v>
+        <v>195</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>468</v>
+        <v>21</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>21</v>
@@ -9867,10 +9885,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9893,13 +9911,13 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>470</v>
+        <v>226</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9926,13 +9944,13 @@
         <v>21</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>21</v>
+        <v>468</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>21</v>
+        <v>469</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>21</v>
@@ -9950,7 +9968,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9959,25 +9977,25 @@
         <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>21</v>
+        <v>471</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>21</v>
+        <v>254</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>444</v>
+        <v>472</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>21</v>
@@ -9985,10 +10003,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9999,7 +10017,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
@@ -10008,16 +10026,16 @@
         <v>21</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10068,7 +10086,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10077,25 +10095,25 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>21</v>
+        <v>470</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>477</v>
+        <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>478</v>
+        <v>21</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>21</v>
+        <v>473</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>21</v>
@@ -10103,10 +10121,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10129,13 +10147,13 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>105</v>
+        <v>479</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>106</v>
+        <v>480</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>107</v>
+        <v>481</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10186,31 +10204,31 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>108</v>
+        <v>478</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>21</v>
+        <v>482</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>21</v>
+        <v>483</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>109</v>
+        <v>484</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>21</v>
@@ -10221,21 +10239,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>21</v>
@@ -10247,17 +10265,15 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -10294,31 +10310,31 @@
         <v>21</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>21</v>
@@ -10341,21 +10357,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
@@ -10364,19 +10380,19 @@
         <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>483</v>
+        <v>112</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>484</v>
+        <v>113</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>485</v>
+        <v>114</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>486</v>
+        <v>115</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10414,31 +10430,31 @@
         <v>21</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>487</v>
+        <v>119</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>21</v>
@@ -10447,10 +10463,10 @@
         <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>488</v>
+        <v>109</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>21</v>
@@ -10461,10 +10477,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10487,15 +10503,17 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>386</v>
+        <v>488</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -10590,10 +10608,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>21</v>
@@ -10605,13 +10623,13 @@
         <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10662,10 +10680,10 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>91</v>
@@ -10686,17 +10704,135 @@
         <v>195</v>
       </c>
       <c r="AN73" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="AO73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP73" t="s" s="2">
+      <c r="B74" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP73">
+  <autoFilter ref="A1:AP74">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10706,7 +10842,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI72">
+  <conditionalFormatting sqref="A2:AI73">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T06:35:14+00:00</t>
+    <t>2026-07-20T14:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:28:37+00:00</t>
+    <t>2026-07-21T08:19:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:19:16+00:00</t>
+    <t>2026-07-21T08:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:48:20+00:00</t>
+    <t>2026-07-21T09:53:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:53:07+00:00</t>
+    <t>2026-07-21T13:00:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:00:05+00:00</t>
+    <t>2026-07-27T06:31:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T06:31:56+00:00</t>
+    <t>2026-07-27T07:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T07:32:14+00:00</t>
+    <t>2026-07-27T07:43:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T07:43:34+00:00</t>
+    <t>2026-07-27T08:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T08:58:26+00:00</t>
+    <t>2026-07-27T09:29:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T09:29:06+00:00</t>
+    <t>2026-07-27T09:54:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T09:54:42+00:00</t>
+    <t>2026-07-27T10:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:14:55+00:00</t>
+    <t>2026-07-27T10:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:27:19+00:00</t>
+    <t>2026-07-27T10:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:49:55+00:00</t>
+    <t>2026-07-28T05:51:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T05:51:13+00:00</t>
+    <t>2026-07-28T06:19:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T06:19:15+00:00</t>
+    <t>2026-07-28T06:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T06:47:20+00:00</t>
+    <t>2026-07-28T13:00:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T13:00:26+00:00</t>
+    <t>2026-07-28T13:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T13:42:50+00:00</t>
+    <t>2026-07-28T14:03:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T14:03:46+00:00</t>
+    <t>2026-07-29T06:44:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T06:44:02+00:00</t>
+    <t>2026-07-29T11:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:08:45+00:00</t>
+    <t>2026-07-29T11:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:32:55+00:00</t>
+    <t>2026-07-29T11:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:56:42+00:00</t>
+    <t>2026-07-30T06:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T06:46:32+00:00</t>
+    <t>2026-07-30T07:01:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:01:31+00:00</t>
+    <t>2026-07-30T10:22:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:22:13+00:00</t>
+    <t>2026-07-31T07:01:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T07:01:03+00:00</t>
+    <t>2026-07-31T08:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:34:12+00:00</t>
+    <t>2026-07-31T10:47:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T10:47:24+00:00</t>
+    <t>2026-07-31T12:19:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:19:34+00:00</t>
+    <t>2026-08-03T09:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T09:14:34+00:00</t>
+    <t>2026-08-03T10:33:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4499,7 +4499,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T10:33:06+00:00</t>
+    <t>2026-08-06T10:46:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:46:09+00:00</t>
+    <t>2026-08-07T07:27:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T07:27:35+00:00</t>
+    <t>2026-08-10T07:07:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T07:07:45+00:00</t>
+    <t>2026-08-10T09:07:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T09:07:49+00:00</t>
+    <t>2026-08-10T10:07:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T10:07:23+00:00</t>
+    <t>2026-08-12T14:05:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T14:05:51+00:00</t>
+    <t>2026-08-12T15:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T15:02:16+00:00</t>
+    <t>2026-08-13T10:03:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T10:03:40+00:00</t>
+    <t>2026-08-14T12:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:06:36+00:00</t>
+    <t>2026-08-20T12:53:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:53:18+00:00</t>
+    <t>2026-08-26T13:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$65</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2844" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="463">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:50:30+00:00</t>
+    <t>2026-08-28T05:58:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -335,349 +335,175 @@
 </t>
   </si>
   <si>
-    <t>Condition.meta.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
+    <t>Condition.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Condition.meta.extension</t>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>Condition.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>Condition.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>Condition.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Condition.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Condition.extension:reported</t>
+  </si>
+  <si>
+    <t>reported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-reported}
+</t>
+  </si>
+  <si>
+    <t>AT ELGA Reported (Fremdangabe)</t>
+  </si>
+  <si>
+    <t>Kennzeichnet, ob eine Information fremdberichtet ist (z. B. vom Patienten oder Dritten).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Condition.extension:entered-in-error</t>
+  </si>
+  <si>
+    <t>entered-in-error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-ext-entered-in-error}
+</t>
+  </si>
+  <si>
+    <t>AT ELGA Entered In Error</t>
+  </si>
+  <si>
+    <t>Kennzeichnet, ob eine Information fehlerhaft eingegeben wurde.</t>
+  </si>
+  <si>
+    <t>Condition.modifierExtension</t>
   </si>
   <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Condition.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>Condition.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>Condition.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>Condition.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Condition.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>Condition.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:$this}
-</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>Condition.meta.tag:diagnosisType</t>
-  </si>
-  <si>
-    <t>diagnosisType</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-diagnosen-type</t>
-  </si>
-  <si>
-    <t>Condition.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>Condition.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>Condition.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>Condition.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Condition.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>Condition.extension:reported</t>
-  </si>
-  <si>
-    <t>reported</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-reported}
-</t>
-  </si>
-  <si>
-    <t>AT ELGA Reported (Fremdangabe)</t>
-  </si>
-  <si>
-    <t>Kennzeichnet, ob eine Information fremdberichtet ist (z. B. vom Patienten oder Dritten).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>Condition.extension:entered-in-error</t>
-  </si>
-  <si>
-    <t>entered-in-error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-ext-entered-in-error}
-</t>
-  </si>
-  <si>
-    <t>AT ELGA Entered In Error</t>
-  </si>
-  <si>
-    <t>Kennzeichnet, ob eine Information fehlerhaft eingegeben wurde.</t>
-  </si>
-  <si>
-    <t>Condition.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -685,6 +511,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -736,6 +565,9 @@
     <t>The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
+    <t>required</t>
+  </si>
+  <si>
     <t>The clinical status of the condition or diagnosis.</t>
   </si>
   <si>
@@ -801,13 +633,16 @@
     <t>Condition.category</t>
   </si>
   <si>
-    <t>Differenzierung nach Kontext - wird meta.tag gelöst</t>
+    <t>Differenzierung nach Kontext ist nicht relevant.</t>
   </si>
   <si>
     <t>A category assigned to the condition.</t>
   </si>
   <si>
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-category|4.0.1</t>
@@ -869,6 +704,9 @@
   </si>
   <si>
     <t>0..1 to account for primarily narrative only resources.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Identification of the condition or diagnosis.</t>
@@ -907,13 +745,45 @@
     <t>Condition.code.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Condition.code.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
     <t>Condition.code.coding</t>
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
   </si>
   <si>
     <t>Code defined by a terminology system</t>
@@ -1919,7 +1789,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP74"/>
+  <dimension ref="A1:AP65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.85546875" customWidth="true" bestFit="true"/>
@@ -1946,8 +1816,8 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.50390625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="73.078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.00390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -2471,10 +2341,10 @@
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>105</v>
@@ -2485,7 +2355,9 @@
       <c r="M5" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="N5" s="2"/>
+      <c r="N5" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>21</v>
@@ -2534,7 +2406,7 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -2546,7 +2418,7 @@
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>21</v>
@@ -2558,7 +2430,7 @@
         <v>21</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>21</v>
@@ -2576,14 +2448,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>21</v>
@@ -2595,16 +2467,16 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2630,43 +2502,43 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="AF6" t="s" s="2">
-        <v>119</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>21</v>
@@ -2678,7 +2550,7 @@
         <v>21</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>21</v>
@@ -2689,14 +2561,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2712,10 +2584,10 @@
         <v>21</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>122</v>
@@ -2798,7 +2670,7 @@
         <v>21</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>21</v>
@@ -2809,21 +2681,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>21</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>21</v>
@@ -2832,19 +2704,19 @@
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2894,19 +2766,19 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>21</v>
@@ -2918,7 +2790,7 @@
         <v>21</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>21</v>
@@ -2929,10 +2801,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2943,7 +2815,7 @@
         <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -2952,20 +2824,18 @@
         <v>21</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>21</v>
@@ -3002,31 +2872,29 @@
         <v>21</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>21</v>
@@ -3049,12 +2917,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="D10" t="s" s="2">
         <v>21</v>
       </c>
@@ -3063,7 +2933,7 @@
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
@@ -3072,20 +2942,18 @@
         <v>21</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
@@ -3134,7 +3002,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3143,10 +3011,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -3169,12 +3037,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>21</v>
       </c>
@@ -3183,7 +3053,7 @@
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -3192,20 +3062,18 @@
         <v>21</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>21</v>
@@ -3230,13 +3098,13 @@
         <v>21</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>21</v>
@@ -3254,7 +3122,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3263,10 +3131,10 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>21</v>
@@ -3289,18 +3157,18 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>81</v>
@@ -3309,24 +3177,26 @@
         <v>21</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O12" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="O12" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>21</v>
       </c>
@@ -3350,29 +3220,31 @@
         <v>21</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AC12" s="2"/>
-      <c r="AD12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3384,7 +3256,7 @@
         <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>21</v>
@@ -3396,7 +3268,7 @@
         <v>21</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>21</v>
@@ -3407,23 +3279,21 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
@@ -3435,18 +3305,20 @@
         <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O13" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>21</v>
       </c>
@@ -3470,11 +3342,13 @@
         <v>21</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z13" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
@@ -3507,7 +3381,7 @@
         <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>21</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>21</v>
@@ -3516,21 +3390,21 @@
         <v>21</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3538,13 +3412,13 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>92</v>
@@ -3553,16 +3427,16 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3588,13 +3462,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3621,36 +3495,36 @@
         <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>21</v>
+        <v>178</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3658,31 +3532,31 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3708,13 +3582,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3732,7 +3606,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3741,47 +3615,47 @@
         <v>91</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>21</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>181</v>
+        <v>21</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
@@ -3793,16 +3667,16 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3828,13 +3702,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>21</v>
+        <v>197</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3852,13 +3726,13 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>21</v>
@@ -3870,16 +3744,16 @@
         <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>21</v>
+        <v>202</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>21</v>
@@ -3887,21 +3761,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -3913,16 +3787,16 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3948,13 +3822,13 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>21</v>
+        <v>207</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
@@ -3972,77 +3846,79 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>21</v>
+        <v>214</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>21</v>
+        <v>216</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>112</v>
+        <v>171</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+      <c r="O18" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
       </c>
@@ -4066,71 +3942,71 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>21</v>
+        <v>221</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC18" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>21</v>
+        <v>223</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>21</v>
+        <v>225</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>21</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>21</v>
       </c>
@@ -4151,13 +4027,13 @@
         <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4208,19 +4084,19 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>233</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>21</v>
@@ -4232,7 +4108,7 @@
         <v>21</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>21</v>
@@ -4243,23 +4119,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -4271,15 +4145,17 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>136</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -4316,19 +4192,19 @@
         <v>21</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>199</v>
+        <v>239</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4337,10 +4213,10 @@
         <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>21</v>
@@ -4352,7 +4228,7 @@
         <v>21</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>21</v>
@@ -4363,45 +4239,45 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>241</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="J21" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>112</v>
+        <v>242</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -4438,19 +4314,17 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4462,7 +4336,7 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>21</v>
@@ -4471,10 +4345,10 @@
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>195</v>
+        <v>251</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>21</v>
@@ -4485,21 +4359,23 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -4511,19 +4387,19 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4572,7 +4448,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4587,30 +4463,30 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4618,32 +4494,30 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4668,13 +4542,13 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4692,7 +4566,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4701,68 +4575,68 @@
         <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>232</v>
+        <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>233</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AM23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>236</v>
-      </c>
       <c r="AO23" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>241</v>
+        <v>158</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4788,69 +4662,69 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>233</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4858,10 +4732,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -4870,27 +4744,29 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>226</v>
+        <v>105</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>21</v>
@@ -4908,13 +4784,13 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>251</v>
+        <v>21</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>253</v>
+        <v>21</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
@@ -4932,13 +4808,13 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
@@ -4950,16 +4826,16 @@
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>254</v>
+        <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>257</v>
+        <v>21</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>21</v>
@@ -4967,10 +4843,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4981,7 +4857,7 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
@@ -4990,19 +4866,19 @@
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5028,13 +4904,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>260</v>
+        <v>21</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>262</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -5052,7 +4928,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5070,31 +4946,31 @@
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>263</v>
+        <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>266</v>
+        <v>21</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>267</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5104,7 +4980,7 @@
         <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
@@ -5113,17 +4989,17 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>226</v>
+        <v>111</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -5148,13 +5024,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>274</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -5172,7 +5048,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5187,30 +5063,30 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>276</v>
+        <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>280</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5230,19 +5106,21 @@
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>105</v>
+        <v>230</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>106</v>
+        <v>286</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>107</v>
+        <v>287</v>
       </c>
       <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+      <c r="O28" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
@@ -5290,7 +5168,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>108</v>
+        <v>289</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5302,7 +5180,7 @@
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>21</v>
@@ -5311,10 +5189,10 @@
         <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>109</v>
+        <v>291</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>21</v>
@@ -5325,21 +5203,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -5348,21 +5226,23 @@
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>112</v>
+        <v>294</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>113</v>
+        <v>295</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>114</v>
+        <v>296</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -5398,31 +5278,31 @@
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>119</v>
+        <v>299</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
@@ -5431,10 +5311,10 @@
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>21</v>
+        <v>300</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>109</v>
+        <v>301</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>21</v>
@@ -5445,21 +5325,23 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G30" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -5471,19 +5353,19 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>145</v>
+        <v>242</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>285</v>
+        <v>243</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>286</v>
+        <v>244</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>287</v>
+        <v>245</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5520,17 +5402,19 @@
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AC30" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>290</v>
+        <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>291</v>
+        <v>249</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5551,10 +5435,10 @@
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>292</v>
+        <v>250</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>293</v>
+        <v>251</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>21</v>
@@ -5565,20 +5449,18 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>91</v>
@@ -5590,23 +5472,19 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>145</v>
+        <v>230</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>285</v>
+        <v>231</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5654,19 +5532,19 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>291</v>
+        <v>233</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>21</v>
@@ -5675,10 +5553,10 @@
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>292</v>
+        <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>293</v>
+        <v>234</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>21</v>
@@ -5689,21 +5567,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>257</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5715,15 +5593,17 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>106</v>
+        <v>236</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5760,31 +5640,31 @@
         <v>21</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>108</v>
+        <v>239</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
@@ -5796,7 +5676,7 @@
         <v>21</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>109</v>
+        <v>234</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>21</v>
@@ -5807,21 +5687,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>299</v>
+        <v>259</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5830,27 +5710,29 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>113</v>
+        <v>260</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>114</v>
+        <v>261</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>21</v>
+        <v>307</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>21</v>
@@ -5880,31 +5762,31 @@
         <v>21</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>119</v>
+        <v>265</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
@@ -5913,10 +5795,10 @@
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>21</v>
+        <v>266</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>109</v>
+        <v>267</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>21</v>
@@ -5927,10 +5809,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5938,7 +5820,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>91</v>
@@ -5953,26 +5835,24 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>133</v>
+        <v>230</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>302</v>
+        <v>270</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>303</v>
+        <v>271</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>306</v>
+        <v>21</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>21</v>
@@ -6014,7 +5894,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>307</v>
+        <v>273</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6035,10 +5915,10 @@
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>308</v>
+        <v>274</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>309</v>
+        <v>275</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
@@ -6049,10 +5929,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>311</v>
+        <v>277</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6060,7 +5940,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>91</v>
@@ -6075,18 +5955,18 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>312</v>
+        <v>278</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -6134,7 +6014,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>315</v>
+        <v>281</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6155,10 +6035,10 @@
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>316</v>
+        <v>282</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>317</v>
+        <v>283</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>21</v>
@@ -6169,10 +6049,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>319</v>
+        <v>285</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6180,7 +6060,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>91</v>
@@ -6195,17 +6075,17 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>320</v>
+        <v>286</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>321</v>
+        <v>287</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>322</v>
+        <v>288</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -6254,7 +6134,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>323</v>
+        <v>289</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6275,10 +6155,10 @@
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>324</v>
+        <v>290</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>325</v>
+        <v>291</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
@@ -6289,10 +6169,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>327</v>
+        <v>293</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6315,17 +6195,19 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>105</v>
+        <v>294</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>328</v>
+        <v>295</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O37" t="s" s="2">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6374,7 +6256,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>331</v>
+        <v>299</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6395,10 +6277,10 @@
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>333</v>
+        <v>301</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -6409,10 +6291,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6423,7 +6305,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>21</v>
@@ -6435,19 +6317,19 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>336</v>
+        <v>230</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6496,7 +6378,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>341</v>
+        <v>317</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6517,10 +6399,10 @@
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>342</v>
+        <v>318</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>343</v>
+        <v>319</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
@@ -6531,14 +6413,12 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6547,7 +6427,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -6559,20 +6439,18 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6596,13 +6474,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>21</v>
+        <v>324</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>21</v>
+        <v>325</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6620,7 +6498,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6638,59 +6516,61 @@
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>21</v>
+        <v>326</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>292</v>
+        <v>21</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>21</v>
+        <v>330</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>105</v>
+        <v>331</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>106</v>
+        <v>332</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>107</v>
+        <v>333</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6738,10 +6618,10 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>108</v>
+        <v>329</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>91</v>
@@ -6750,22 +6630,22 @@
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>21</v>
+        <v>335</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>21</v>
+        <v>336</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>109</v>
+        <v>337</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>21</v>
+        <v>338</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>21</v>
@@ -6773,21 +6653,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>299</v>
+        <v>339</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6796,19 +6676,19 @@
         <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>112</v>
+        <v>340</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>113</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>114</v>
+        <v>342</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>115</v>
+        <v>343</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6846,46 +6726,46 @@
         <v>21</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>119</v>
+        <v>339</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>21</v>
+        <v>344</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>109</v>
+        <v>346</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>21</v>
+        <v>347</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>21</v>
@@ -6896,7 +6776,7 @@
         <v>348</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>301</v>
+        <v>348</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6904,7 +6784,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>91</v>
@@ -6919,26 +6799,24 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>133</v>
+        <v>349</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>302</v>
+        <v>350</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>303</v>
+        <v>351</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>349</v>
+        <v>21</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>21</v>
@@ -6980,7 +6858,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6995,19 +6873,19 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>21</v>
+        <v>353</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>308</v>
+        <v>354</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>309</v>
+        <v>355</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>21</v>
+        <v>356</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>21</v>
@@ -7015,10 +6893,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7038,19 +6916,19 @@
         <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>105</v>
+        <v>349</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>312</v>
+        <v>358</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>313</v>
+        <v>359</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>314</v>
+        <v>360</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7100,7 +6978,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>315</v>
+        <v>357</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7109,7 +6987,7 @@
         <v>91</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>103</v>
@@ -7121,24 +6999,24 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>316</v>
+        <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>317</v>
+        <v>362</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>319</v>
+        <v>364</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7152,7 +7030,7 @@
         <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -7161,18 +7039,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>172</v>
+        <v>349</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>320</v>
+        <v>365</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>321</v>
+        <v>366</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>322</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -7220,7 +7096,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>323</v>
+        <v>364</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7241,24 +7117,24 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>324</v>
+        <v>367</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>325</v>
+        <v>368</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>21</v>
+        <v>369</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>327</v>
+        <v>370</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7266,13 +7142,13 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
@@ -7281,18 +7157,16 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>105</v>
+        <v>371</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>328</v>
+        <v>372</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>329</v>
+        <v>373</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>330</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -7340,7 +7214,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>331</v>
+        <v>370</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7361,13 +7235,13 @@
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>332</v>
+        <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>333</v>
+        <v>374</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>21</v>
+        <v>375</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>21</v>
@@ -7375,10 +7249,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>335</v>
+        <v>376</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7401,20 +7275,16 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>336</v>
+        <v>377</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>337</v>
+        <v>378</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7462,7 +7332,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>341</v>
+        <v>376</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7483,13 +7353,13 @@
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>343</v>
+        <v>381</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>21</v>
+        <v>382</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>21</v>
@@ -7497,10 +7367,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7520,23 +7390,19 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>105</v>
+        <v>384</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7584,19 +7450,19 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>103</v>
+        <v>387</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>21</v>
@@ -7605,10 +7471,10 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>21</v>
@@ -7619,10 +7485,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7633,7 +7499,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -7642,20 +7508,18 @@
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>363</v>
+        <v>231</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7680,13 +7544,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>366</v>
+        <v>21</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>367</v>
+        <v>21</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7704,79 +7568,79 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>362</v>
+        <v>233</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>368</v>
+        <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>369</v>
+        <v>234</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>370</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>372</v>
+        <v>155</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>373</v>
+        <v>136</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>374</v>
+        <v>236</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7824,34 +7688,34 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>371</v>
+        <v>239</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>377</v>
+        <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>379</v>
+        <v>234</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>21</v>
@@ -7859,44 +7723,46 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>382</v>
+        <v>136</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7944,34 +7810,34 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>386</v>
+        <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>387</v>
+        <v>21</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>388</v>
+        <v>134</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>389</v>
+        <v>21</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>21</v>
@@ -7979,10 +7845,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8002,20 +7868,18 @@
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>391</v>
+        <v>171</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -8040,13 +7904,13 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>21</v>
+        <v>399</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>21</v>
+        <v>400</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -8064,7 +7928,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8073,25 +7937,25 @@
         <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>21</v>
+        <v>402</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>396</v>
+        <v>181</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>397</v>
+        <v>226</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>398</v>
+        <v>21</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>21</v>
@@ -8099,10 +7963,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8113,7 +7977,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -8125,17 +7989,15 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8184,16 +8046,16 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>103</v>
@@ -8208,21 +8070,21 @@
         <v>21</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>405</v>
+        <v>21</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8230,28 +8092,28 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>391</v>
+        <v>171</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8278,13 +8140,13 @@
         <v>21</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>21</v>
+        <v>411</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>21</v>
+        <v>412</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -8302,7 +8164,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8323,24 +8185,24 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>409</v>
+        <v>21</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>411</v>
+        <v>21</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8348,30 +8210,32 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>413</v>
+        <v>384</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8420,19 +8284,19 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>103</v>
+        <v>418</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
@@ -8444,10 +8308,10 @@
         <v>21</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>417</v>
+        <v>21</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>21</v>
@@ -8455,10 +8319,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8478,16 +8342,16 @@
         <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>419</v>
+        <v>230</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>420</v>
+        <v>231</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>421</v>
+        <v>232</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8538,7 +8402,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>418</v>
+        <v>233</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8550,7 +8414,7 @@
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
@@ -8559,13 +8423,13 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>423</v>
+        <v>234</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>424</v>
+        <v>21</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>21</v>
@@ -8573,21 +8437,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
@@ -8599,15 +8463,17 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>426</v>
+        <v>136</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>427</v>
+        <v>236</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8656,7 +8522,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>425</v>
+        <v>239</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8668,7 +8534,7 @@
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>429</v>
+        <v>142</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
@@ -8680,7 +8546,7 @@
         <v>21</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>430</v>
+        <v>234</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>21</v>
@@ -8691,42 +8557,46 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>106</v>
+        <v>393</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8774,19 +8644,19 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>108</v>
+        <v>395</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
@@ -8798,7 +8668,7 @@
         <v>21</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
@@ -8809,14 +8679,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8832,20 +8702,18 @@
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>112</v>
+        <v>171</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>113</v>
+        <v>424</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8870,13 +8738,13 @@
         <v>21</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>21</v>
@@ -8894,7 +8762,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>119</v>
+        <v>423</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8903,25 +8771,25 @@
         <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>21</v>
+        <v>429</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>109</v>
+        <v>430</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>21</v>
+        <v>431</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>21</v>
@@ -8929,14 +8797,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>434</v>
+        <v>21</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8949,26 +8817,22 @@
         <v>21</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>112</v>
+        <v>433</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>214</v>
-      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -9016,7 +8880,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9025,10 +8889,10 @@
         <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
@@ -9040,10 +8904,10 @@
         <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>195</v>
+        <v>407</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>21</v>
+        <v>431</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>21</v>
@@ -9051,10 +8915,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9077,13 +8941,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>226</v>
+        <v>437</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9110,13 +8974,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>441</v>
+        <v>21</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>442</v>
+        <v>21</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9134,31 +8998,31 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>443</v>
+        <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>21</v>
+        <v>440</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>444</v>
+        <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>235</v>
+        <v>441</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>278</v>
+        <v>442</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>21</v>
@@ -9169,10 +9033,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9183,7 +9047,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -9195,13 +9059,13 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>446</v>
+        <v>230</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>447</v>
+        <v>231</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>448</v>
+        <v>232</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9252,19 +9116,19 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>445</v>
+        <v>233</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>443</v>
+        <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
@@ -9276,7 +9140,7 @@
         <v>21</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>449</v>
+        <v>234</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>21</v>
@@ -9287,21 +9151,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -9313,15 +9177,17 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>451</v>
+        <v>236</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9346,43 +9212,43 @@
         <v>21</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>453</v>
+        <v>21</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>454</v>
+        <v>21</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>450</v>
+        <v>239</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>21</v>
@@ -9394,7 +9260,7 @@
         <v>21</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>455</v>
+        <v>234</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>21</v>
@@ -9405,10 +9271,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9419,7 +9285,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
@@ -9428,19 +9294,19 @@
         <v>21</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9490,19 +9356,19 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>460</v>
+        <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
@@ -9511,10 +9377,10 @@
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>21</v>
@@ -9525,10 +9391,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9539,7 +9405,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>21</v>
@@ -9548,16 +9414,16 @@
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>105</v>
+        <v>349</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>106</v>
+        <v>453</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>107</v>
+        <v>454</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9608,7 +9474,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>108</v>
+        <v>455</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9620,7 +9486,7 @@
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
@@ -9629,10 +9495,10 @@
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>109</v>
+        <v>456</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>21</v>
@@ -9643,21 +9509,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -9666,20 +9532,18 @@
         <v>21</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>112</v>
+        <v>458</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>113</v>
+        <v>459</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -9728,19 +9592,19 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>119</v>
+        <v>461</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>21</v>
@@ -9749,1090 +9613,20 @@
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>109</v>
+        <v>462</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP74" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP74">
+  <autoFilter ref="A1:AP65">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10842,7 +9636,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI73">
+  <conditionalFormatting sqref="A2:AI64">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T05:58:13+00:00</t>
+    <t>2026-08-28T07:25:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:25:52+00:00</t>
+    <t>2026-08-28T08:10:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:10:45+00:00</t>
+    <t>2026-08-28T11:38:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1053,7 +1053,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
 </t>
   </si>
   <si>
@@ -1177,7 +1177,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole)
 </t>
   </si>
   <si>
@@ -1196,7 +1196,7 @@
     <t>Condition.asserter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1802,7 +1802,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="198.703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="213.203125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T11:38:22+00:00</t>
+    <t>2026-08-28T12:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:52:33+00:00</t>
+    <t>2026-08-31T10:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:02:50+00:00</t>
+    <t>2026-09-01T06:51:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T06:51:10+00:00</t>
+    <t>2026-09-01T11:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:42:45+00:00</t>
+    <t>2026-09-01T12:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:48:31+00:00</t>
+    <t>2026-09-01T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:57:21+00:00</t>
+    <t>2026-09-03T13:31:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T13:31:10+00:00</t>
+    <t>2026-09-07T04:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T04:47:29+00:00</t>
+    <t>2026-09-07T06:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T06:52:33+00:00</t>
+    <t>2026-09-07T07:43:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T07:43:01+00:00</t>
+    <t>2026-09-07T07:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T07:56:25+00:00</t>
+    <t>2026-09-07T09:23:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T09:23:06+00:00</t>
+    <t>2026-09-07T10:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:17:45+00:00</t>
+    <t>2026-09-07T10:50:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -527,7 +527,7 @@
 </t>
   </si>
   <si>
-    <t>Zuordnung der Diagnose in einem internem Dokumentationssystem</t>
+    <t>Zuordnung der Diagnose in einem internen Dokumentationssystem</t>
   </si>
   <si>
     <t>Business identifiers assigned to this condition by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
@@ -555,8 +555,7 @@
 </t>
   </si>
   <si>
-    <t>Klinischer Status der Diagnose (wie:Status post), 
-mögliche Codes: active | recurrence | relapse | inactive | remission | resolved</t>
+    <t>Klinischer Status der Diagnose (wie:Status post), mögliche Codes: active | recurrence | relapse | inactive | remission | resolved</t>
   </si>
   <si>
     <t>The clinical status of the condition.</t>
@@ -597,7 +596,7 @@
     <t>Condition.verificationStatus</t>
   </si>
   <si>
-    <t>Status der Diagnose, mögliche Codes: unconfirmed | provisional | differential | confirmed | refuted | entered-in-error</t>
+    <t>Verifizierungsstatus der Diagnose, mögliche Codes: unconfirmed | provisional | differential | confirmed | refuted | entered-in-error</t>
   </si>
   <si>
     <t>The verification status to support the clinical status of the condition.</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:50:55+00:00</t>
+    <t>2026-09-08T06:03:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:03:03+00:00</t>
+    <t>2026-09-08T06:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:16:43+00:00</t>
+    <t>2026-09-08T06:28:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -527,7 +527,7 @@
 </t>
   </si>
   <si>
-    <t>Zuordnung der Diagnose in einem internen Dokumentationssystem</t>
+    <t>Zuordnung der Diagnose in einem internen Dokumentationssystem.</t>
   </si>
   <si>
     <t>Business identifiers assigned to this condition by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
@@ -555,7 +555,7 @@
 </t>
   </si>
   <si>
-    <t>Klinischer Status der Diagnose (wie:Status post), mögliche Codes: active | recurrence | relapse | inactive | remission | resolved</t>
+    <t>Klinischer Status der Diagnose (z. B. Status post); mögliche Codes: active | recurrence | relapse | inactive | remission | resolved.</t>
   </si>
   <si>
     <t>The clinical status of the condition.</t>
@@ -596,7 +596,7 @@
     <t>Condition.verificationStatus</t>
   </si>
   <si>
-    <t>Verifizierungsstatus der Diagnose, mögliche Codes: unconfirmed | provisional | differential | confirmed | refuted | entered-in-error</t>
+    <t>Verifizierungsstatus der Diagnose, mögliche Codes: unconfirmed | provisional | differential | confirmed | refuted | entered-in-error.</t>
   </si>
   <si>
     <t>The verification status to support the clinical status of the condition.</t>
@@ -662,7 +662,7 @@
     <t>Condition.severity</t>
   </si>
   <si>
-    <t>Schweregrad der Erkrankung</t>
+    <t>Schweregrad der Erkrankung.</t>
   </si>
   <si>
     <t>A subjective assessment of the severity of the condition as evaluated by the clinician.</t>
@@ -696,7 +696,7 @@
 </t>
   </si>
   <si>
-    <t>Diagnosecode (Codierservice), Text verboten, Codesystem 1.SNOMED 2.Orphanet</t>
+    <t>Diagnosecode (Codierservice); Freitext ist nicht zulässig. Codesysteme: 1. SNOMED CT, 2. Orphanet.</t>
   </si>
   <si>
     <t>Identification of the condition, problem or diagnosis.</t>
@@ -1021,7 +1021,7 @@
     <t>Condition.bodySite</t>
   </si>
   <si>
-    <t>Zuordnung der Diagnose der Körper-Lokalisation</t>
+    <t>Zuordnung der Diagnose zu einer Körperstelle.</t>
   </si>
   <si>
     <t>The anatomical location where this condition manifests itself.</t>
@@ -1056,7 +1056,7 @@
 </t>
   </si>
   <si>
-    <t>Person, auf die sich die Diagnose bezieht</t>
+    <t>Person, auf die sich die Diagnose bezieht.</t>
   </si>
   <si>
     <t>Indicates the patient or group who the condition record is associated with.</t>
@@ -1084,7 +1084,7 @@
 </t>
   </si>
   <si>
-    <t>Behandlungskontakt</t>
+    <t>Behandlungskontakt.</t>
   </si>
   <si>
     <t>The Encounter during which this Condition was created or to which the creation of this record is tightly associated.</t>
@@ -1112,7 +1112,7 @@
 </t>
   </si>
   <si>
-    <t>Beginn der Erkrankung/Diagnosezeitpunkt</t>
+    <t>Beginn der Erkrankung bzw. Diagnosezeitpunkt.</t>
   </si>
   <si>
     <t>Estimated or actual date or date-time  the condition began, in the opinion of the clinician.</t>
@@ -1136,7 +1136,7 @@
     <t>Condition.abatement[x]</t>
   </si>
   <si>
-    <t>Ende der Erkrankung</t>
+    <t>Ende der Erkrankung.</t>
   </si>
   <si>
     <t>The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
@@ -1158,7 +1158,7 @@
     <t>Condition.recordedDate</t>
   </si>
   <si>
-    <t>Zeitpunkt der Diagnosendokumentation</t>
+    <t>Zeitpunkt der Dokumentation der Diagnose.</t>
   </si>
   <si>
     <t>The recordedDate represents when this particular Condition record was created in the system, which is often a system-generated date.</t>
@@ -1180,7 +1180,7 @@
 </t>
   </si>
   <si>
-    <t>Ansonsten Gesundheitsdiensteanbieter, der die Diagnose eingetragen hat</t>
+    <t>GDA, der die Diagnose eingetragen hat.</t>
   </si>
   <si>
     <t>Individual who recorded the record and takes responsibility for its content.</t>
@@ -1199,7 +1199,7 @@
 </t>
   </si>
   <si>
-    <t>Quelle der Information zur Diagnose (z. B. behandelnde Person, Patient oder Dritter)</t>
+    <t>Quelle der Information zur Diagnose (z. B. behandelnde GDA, Patient oder Dritter).</t>
   </si>
   <si>
     <t>Individual who is making the condition statement.</t>
@@ -1221,7 +1221,7 @@
 </t>
   </si>
   <si>
-    <t>Stadium der Erkrankung</t>
+    <t>Stadium der Erkrankung.</t>
   </si>
   <si>
     <t>Clinical stage or grade of a condition. May include formal severity assessments.</t>
@@ -1316,7 +1316,7 @@
     <t>Condition.evidence</t>
   </si>
   <si>
-    <t>Verweis auf ELGA-Befunde als medizinische Evidenz</t>
+    <t>Verweis auf ELGA-Befunde als medizinische Evidenz.</t>
   </si>
   <si>
     <t>Supporting evidence / manifestations that are the basis of the Condition's verification status, such as evidence that confirmed or refuted the condition.</t>
@@ -1389,7 +1389,7 @@
 </t>
   </si>
   <si>
-    <t>Freitext zur Diagnose für Zusatzinformation</t>
+    <t>Freitext zur Diagnose als Zusatzinformation.</t>
   </si>
   <si>
     <t>Additional information about the Condition. This is a general notes/comments entry  for description of the Condition, its diagnosis and prognosis.</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:28:20+00:00</t>
+    <t>2026-09-08T06:46:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:46:13+00:00</t>
+    <t>2026-09-08T10:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:19:13+00:00</t>
+    <t>2026-09-08T10:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:46:31+00:00</t>
+    <t>2026-09-08T11:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:50:41+00:00</t>
+    <t>2026-09-08T12:56:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T12:56:54+00:00</t>
+    <t>2026-09-09T04:29:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T04:29:28+00:00</t>
+    <t>2026-09-09T07:41:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T07:41:46+00:00</t>
+    <t>2026-09-09T08:03:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T08:03:40+00:00</t>
+    <t>2026-09-09T09:18:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T09:18:29+00:00</t>
+    <t>2026-09-09T14:48:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:48:33+00:00</t>
+    <t>2026-09-10T08:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T08:40:11+00:00</t>
+    <t>2026-09-10T09:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:01:10+00:00</t>
+    <t>2026-09-10T09:35:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:35:03+00:00</t>
+    <t>2026-09-10T09:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:50:09+00:00</t>
+    <t>2026-09-10T10:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:02:23+00:00</t>
+    <t>2026-09-10T11:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:15:10+00:00</t>
+    <t>2026-09-10T11:24:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:24:50+00:00</t>
+    <t>2026-09-10T11:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:47:23+00:00</t>
+    <t>2026-09-10T14:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T14:22:40+00:00</t>
+    <t>2026-09-11T07:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T07:57:50+00:00</t>
+    <t>2026-09-11T08:25:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
